--- a/for-neo4j/cidoc-kg-def3.xlsx
+++ b/for-neo4j/cidoc-kg-def3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rayz/Downloads/yuki-cidoc-proj/for-neo4j/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98EAD6E-E500-1C40-AEAC-2840F78CCA67}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A7B2EB-AF51-F148-9B06-2C99C13C890B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="2460" windowWidth="28460" windowHeight="16480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-8380" yWindow="-26300" windowWidth="48680" windowHeight="24440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cidoc概念关联" sheetId="1" r:id="rId1"/>
@@ -270,10 +270,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>陶器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>关联到该文物的制造活动。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -300,9 +296,6 @@
   <si>
     <t>量度信息</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>记录其长、宽、高、重等定量数据。</t>
   </si>
   <si>
     <t>记录其长、宽、高、重等定量数据。</t>
@@ -370,10 +363,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>玉器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>P2 has type(有类型)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -529,10 +518,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>遗址</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>E27 Site</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -684,10 +669,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>时期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>E4 Period</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -793,6 +774,26 @@
   </si>
   <si>
     <t>将物理实体（墓葬/灰坑/地层/堆积等）归属到特定时期/期别，如将物理地层（第3层）归属到特定期别（第二期）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E55 Type (类型)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陶器 pottery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玉器 jade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遗址 site</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时期 period</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -800,7 +801,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -814,12 +815,6 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -901,45 +896,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1224,7 +1216,7 @@
   <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" style="7" customWidth="1"/>
     <col min="2" max="2" width="44.1640625" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="39.83203125" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="44.1640625" style="12" bestFit="1" customWidth="1"/>
@@ -1240,7 +1232,7 @@
         <v>71</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1249,24 +1241,24 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>2</v>
@@ -1289,19 +1281,19 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>59</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>53</v>
@@ -1315,19 +1307,19 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>53</v>
@@ -1341,19 +1333,19 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>60</v>
@@ -1367,19 +1359,19 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>10</v>
@@ -1393,10 +1385,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>13</v>
@@ -1419,19 +1411,19 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>18</v>
@@ -1445,10 +1437,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>21</v>
@@ -1471,10 +1463,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>26</v>
@@ -1492,15 +1484,15 @@
         <v>28</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>9</v>
@@ -1523,19 +1515,19 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>31</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>18</v>
@@ -1549,10 +1541,10 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>13</v>
@@ -1575,10 +1567,10 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>13</v>
@@ -1601,10 +1593,10 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>13</v>
@@ -1615,8 +1607,8 @@
       <c r="E15" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="14" t="s">
-        <v>80</v>
+      <c r="F15" s="10" t="s">
+        <v>197</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>39</v>
@@ -1627,10 +1619,10 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>41</v>
@@ -1653,19 +1645,19 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>47</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>61</v>
@@ -1679,19 +1671,19 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>48</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>14</v>
@@ -1700,310 +1692,310 @@
         <v>70</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>49</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>62</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>50</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>63</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>51</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>64</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>58</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>65</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>66</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>57</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>67</v>
       </c>
       <c r="G24" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G25" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" s="10" t="s">
+      <c r="H25" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="3" t="s">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C26" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="G26" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="H26" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="3" t="s">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C27" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F27" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="G27" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="H27" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="3" t="s">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C28" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="3" t="s">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C29" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="G29" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="H29" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="3" t="s">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>47</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F30" s="10" t="s">
         <v>61</v>
@@ -2017,71 +2009,71 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="3" t="s">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>67</v>
       </c>
       <c r="G31" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="H31" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="3" t="s">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>58</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>65</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="3" t="s">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>48</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>14</v>
@@ -2090,579 +2082,579 @@
         <v>70</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="3" t="s">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C34" s="10" t="s">
         <v>49</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F34" s="10" t="s">
         <v>62</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="3" t="s">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C35" s="10" t="s">
         <v>50</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>63</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="3" t="s">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>51</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F36" s="10" t="s">
         <v>64</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="3" t="s">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C37" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>66</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="3" t="s">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>23</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="3" t="s">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C39" s="10" t="s">
         <v>31</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G39" s="9" t="s">
         <v>32</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="G40" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="H40" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F40" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="H40" s="10" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="8" t="s">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="B41" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>139</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F41" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="8" t="s">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="8" t="s">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="8" t="s">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="8" t="s">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="8" t="s">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="B46" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="H46" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F46" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="8" t="s">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="8" t="s">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F48" s="10" t="s">
         <v>65</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="3" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="G50" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="H50" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F50" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="3" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="3" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="B52" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C52" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="C52" s="10" t="s">
-        <v>185</v>
-      </c>
       <c r="D52" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="3" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="3" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="3" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>65</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
